--- a/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$106</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4055" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4093" uniqueCount="678">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T10:00:28+00:00</t>
+    <t>2025-07-07T12:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -674,6 +674,22 @@
   <si>
     <t>Motif de la mesure
 Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
+  </si>
+  <si>
+    <t>Observation.extension:MesOriginOfData</t>
+  </si>
+  <si>
+    <t>MesOriginOfData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
+</t>
+  </si>
+  <si>
+    <t>Origine de la donnée</t>
+  </si>
+  <si>
+    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -2430,7 +2446,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP105"/>
+  <dimension ref="A1:AP106"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.26953125" customWidth="true" bestFit="true"/>
@@ -4883,43 +4899,41 @@
         <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="D21" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>114</v>
+        <v>213</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4967,7 +4981,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4991,7 +5005,7 @@
         <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -5009,7 +5023,7 @@
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -5022,23 +5036,25 @@
         <v>82</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O22" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -5087,7 +5103,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5099,22 +5115,22 @@
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>222</v>
+        <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -5122,14 +5138,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5148,17 +5164,17 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -5207,7 +5223,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5222,19 +5238,19 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>82</v>
+        <v>229</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -5242,14 +5258,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5268,18 +5284,18 @@
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -5327,7 +5343,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5342,16 +5358,16 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5362,46 +5378,44 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>82</v>
+        <v>240</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>173</v>
+        <v>241</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="M25" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>247</v>
-      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5425,11 +5439,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>249</v>
+        <v>82</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5447,13 +5463,13 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
@@ -5462,19 +5478,19 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>251</v>
+        <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -5482,10 +5498,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5496,31 +5512,31 @@
         <v>93</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>94</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>256</v>
+        <v>173</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5545,35 +5561,35 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="AC26" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
@@ -5582,19 +5598,19 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>82</v>
+        <v>255</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5602,14 +5618,12 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5618,7 +5632,7 @@
         <v>93</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>94</v>
@@ -5630,19 +5644,19 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5670,28 +5684,26 @@
         <v>177</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5715,10 +5727,10 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5726,24 +5738,26 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>82</v>
@@ -5752,16 +5766,20 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>107</v>
+        <v>261</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>108</v>
+        <v>262</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5785,13 +5803,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5809,19 +5827,19 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5833,10 +5851,10 @@
         <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>111</v>
+        <v>269</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>82</v>
+        <v>270</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5844,21 +5862,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5870,17 +5888,15 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5917,31 +5933,31 @@
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5964,46 +5980,44 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>274</v>
+        <v>115</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>275</v>
+        <v>116</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -6039,19 +6053,19 @@
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>278</v>
+        <v>121</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6063,7 +6077,7 @@
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
@@ -6072,10 +6086,10 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>279</v>
+        <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>280</v>
+        <v>111</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -6086,10 +6100,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6097,31 +6111,35 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>108</v>
+        <v>279</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -6169,19 +6187,19 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>110</v>
+        <v>283</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6190,10 +6208,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>111</v>
+        <v>285</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -6204,21 +6222,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -6230,17 +6248,15 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -6277,31 +6293,31 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6324,52 +6340,50 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>287</v>
+        <v>115</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>288</v>
+        <v>116</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>82</v>
@@ -6399,31 +6413,31 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>292</v>
+        <v>121</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -6432,10 +6446,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>293</v>
+        <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>294</v>
+        <v>111</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6446,10 +6460,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6457,13 +6471,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
@@ -6472,24 +6486,26 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>82</v>
+        <v>296</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>82</v>
@@ -6531,7 +6547,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6552,10 +6568,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6566,10 +6582,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6577,13 +6593,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
@@ -6592,24 +6608,24 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>308</v>
+        <v>82</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6651,7 +6667,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6672,10 +6688,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6686,10 +6702,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6697,13 +6713,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
@@ -6712,24 +6728,24 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>82</v>
@@ -6771,7 +6787,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6792,10 +6808,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6806,10 +6822,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6832,19 +6848,17 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>322</v>
+        <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6893,7 +6907,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6914,10 +6928,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6928,10 +6942,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6954,19 +6968,19 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>107</v>
+        <v>327</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -7015,7 +7029,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7036,10 +7050,10 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -7050,24 +7064,24 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>340</v>
+        <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
@@ -7076,19 +7090,19 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>256</v>
+        <v>107</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -7113,13 +7127,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -7137,10 +7151,10 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>93</v>
@@ -7152,62 +7166,66 @@
         <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>107</v>
+        <v>261</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>108</v>
+        <v>346</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -7231,13 +7249,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>82</v>
+        <v>350</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -7255,10 +7273,10 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>110</v>
+        <v>344</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>93</v>
@@ -7267,44 +7285,44 @@
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>82</v>
+        <v>354</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>111</v>
+        <v>355</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>82</v>
+        <v>356</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -7316,17 +7334,15 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7363,31 +7379,31 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -7410,18 +7426,18 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>81</v>
@@ -7433,23 +7449,21 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>274</v>
+        <v>115</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>275</v>
+        <v>116</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7485,9 +7499,11 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AC42" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="AD42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7495,7 +7511,7 @@
         <v>120</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>278</v>
+        <v>121</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7507,7 +7523,7 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7516,10 +7532,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>279</v>
+        <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>280</v>
+        <v>111</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7530,14 +7546,12 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7546,7 +7560,7 @@
         <v>93</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -7561,16 +7575,16 @@
         <v>151</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7607,19 +7621,17 @@
         <v>82</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7640,10 +7652,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7654,18 +7666,20 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="C44" s="2"/>
+      <c r="C44" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>93</v>
@@ -7677,19 +7691,23 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>108</v>
+        <v>279</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7737,19 +7755,19 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>110</v>
+        <v>283</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7758,10 +7776,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>111</v>
+        <v>285</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7772,21 +7790,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7798,17 +7816,15 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7845,31 +7861,31 @@
         <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7892,21 +7908,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7915,29 +7931,27 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>287</v>
+        <v>115</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>288</v>
+        <v>116</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>365</v>
+        <v>82</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>82</v>
@@ -7967,31 +7981,31 @@
         <v>82</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>292</v>
+        <v>121</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -8000,10 +8014,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>293</v>
+        <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>294</v>
+        <v>111</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -8014,10 +8028,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8025,7 +8039,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>93</v>
@@ -8040,24 +8054,26 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>82</v>
+        <v>370</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>82</v>
@@ -8099,7 +8115,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8120,10 +8136,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8134,10 +8150,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8145,7 +8161,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>93</v>
@@ -8160,24 +8176,24 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>82</v>
@@ -8219,7 +8235,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8240,10 +8256,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8254,10 +8270,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8265,7 +8281,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>93</v>
@@ -8280,24 +8296,24 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>82</v>
+        <v>375</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>82</v>
@@ -8339,7 +8355,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8360,10 +8376,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8374,10 +8390,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8400,19 +8416,17 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>322</v>
+        <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8461,7 +8475,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8482,10 +8496,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8496,10 +8510,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8522,19 +8536,19 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>107</v>
+        <v>327</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8583,7 +8597,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8604,10 +8618,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8618,10 +8632,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8629,13 +8643,13 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>82</v>
@@ -8644,19 +8658,19 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>377</v>
+        <v>107</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>378</v>
+        <v>337</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>379</v>
+        <v>338</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>380</v>
+        <v>339</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>381</v>
+        <v>340</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8705,7 +8719,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>376</v>
+        <v>341</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8720,19 +8734,19 @@
         <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>382</v>
+        <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>383</v>
+        <v>342</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>384</v>
+        <v>343</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8740,10 +8754,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8751,13 +8765,13 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>82</v>
@@ -8766,18 +8780,20 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8825,13 +8841,13 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
@@ -8840,19 +8856,19 @@
         <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>349</v>
+        <v>388</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8860,21 +8876,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8886,20 +8902,18 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M54" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>398</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8947,13 +8961,13 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
@@ -8962,19 +8976,19 @@
         <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>399</v>
+        <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>400</v>
+        <v>354</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8982,24 +8996,24 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>82</v>
@@ -9008,19 +9022,19 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -9069,7 +9083,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9078,25 +9092,25 @@
         <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>411</v>
+        <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -9104,24 +9118,24 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>82</v>
+        <v>409</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>82</v>
@@ -9130,18 +9144,20 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>129</v>
+        <v>410</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -9189,34 +9205,34 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AG56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>105</v>
-      </c>
       <c r="AK56" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AO56" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -9224,10 +9240,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9238,7 +9254,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -9250,18 +9266,18 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L57" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" t="s" s="2">
-        <v>427</v>
-      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9309,13 +9325,13 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
@@ -9324,19 +9340,19 @@
         <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>428</v>
+        <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -9344,10 +9360,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9358,10 +9374,10 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>82</v>
@@ -9370,19 +9386,17 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9419,65 +9433,65 @@
         <v>82</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AC58" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>439</v>
+        <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>82</v>
+        <v>433</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>440</v>
+        <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>82</v>
+        <v>436</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>93</v>
@@ -9492,19 +9506,19 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9541,19 +9555,17 @@
         <v>82</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="AC59" s="2"/>
       <c r="AD59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9562,7 +9574,7 @@
         <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>105</v>
@@ -9571,59 +9583,65 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C60" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="D60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>107</v>
+        <v>438</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>108</v>
+        <v>439</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9671,7 +9689,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>110</v>
+        <v>437</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9680,47 +9698,47 @@
         <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>82</v>
+        <v>444</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>111</v>
+        <v>447</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9732,17 +9750,15 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9779,31 +9795,31 @@
         <v>82</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -9826,46 +9842,44 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>452</v>
+        <v>114</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>453</v>
+        <v>115</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>454</v>
+        <v>116</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9901,31 +9915,31 @@
         <v>82</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>457</v>
+        <v>121</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -9934,10 +9948,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>459</v>
+        <v>111</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9948,10 +9962,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9959,83 +9973,83 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>173</v>
+        <v>457</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF63" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="P63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q63" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="R63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10056,10 +10070,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -10070,10 +10084,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10081,37 +10095,39 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I64" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q64" s="2"/>
+      <c r="Q64" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="R64" t="s" s="2">
         <v>82</v>
       </c>
@@ -10131,13 +10147,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>82</v>
+        <v>471</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>82</v>
+        <v>472</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -10155,7 +10171,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10176,10 +10192,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10190,10 +10206,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10216,24 +10232,24 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>82</v>
@@ -10275,7 +10291,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10284,7 +10300,7 @@
         <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>486</v>
+        <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>105</v>
@@ -10296,10 +10312,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10310,10 +10326,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10336,26 +10352,24 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>82</v>
@@ -10397,7 +10411,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10406,7 +10420,7 @@
         <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>82</v>
+        <v>491</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>105</v>
@@ -10418,10 +10432,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10432,10 +10446,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10443,7 +10457,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>93</v>
@@ -10455,29 +10469,29 @@
         <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>256</v>
+        <v>173</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="O67" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>82</v>
+        <v>498</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>82</v>
@@ -10495,13 +10509,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>501</v>
+        <v>82</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>502</v>
+        <v>82</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10519,7 +10533,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10528,7 +10542,7 @@
         <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>105</v>
@@ -10540,10 +10554,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>196</v>
+        <v>482</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10554,10 +10568,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10571,7 +10585,7 @@
         <v>93</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>82</v>
@@ -10580,16 +10594,20 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>107</v>
+        <v>261</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>108</v>
+        <v>502</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10613,13 +10631,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>82</v>
+        <v>506</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>82</v>
+        <v>507</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10637,7 +10655,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>110</v>
+        <v>501</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10646,10 +10664,10 @@
         <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>82</v>
+        <v>508</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
@@ -10658,10 +10676,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>111</v>
+        <v>509</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10672,21 +10690,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -10698,17 +10716,15 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10745,31 +10761,31 @@
         <v>82</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10792,14 +10808,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10815,23 +10831,21 @@
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>274</v>
+        <v>115</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>275</v>
+        <v>116</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10867,19 +10881,19 @@
         <v>82</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>278</v>
+        <v>121</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10891,7 +10905,7 @@
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -10900,10 +10914,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>279</v>
+        <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>280</v>
+        <v>111</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10914,10 +10928,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10928,7 +10942,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
@@ -10937,19 +10951,23 @@
         <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>108</v>
+        <v>279</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -10997,19 +11015,19 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>110</v>
+        <v>283</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -11018,10 +11036,10 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>111</v>
+        <v>285</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11032,21 +11050,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -11058,17 +11076,15 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -11105,31 +11121,31 @@
         <v>82</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
@@ -11152,21 +11168,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>82</v>
@@ -11175,23 +11191,21 @@
         <v>82</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>287</v>
+        <v>115</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>288</v>
+        <v>116</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
@@ -11227,31 +11241,31 @@
         <v>82</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>292</v>
+        <v>121</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -11260,10 +11274,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>293</v>
+        <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>294</v>
+        <v>111</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11274,10 +11288,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11285,7 +11299,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>93</v>
@@ -11300,18 +11314,20 @@
         <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11359,7 +11375,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11380,10 +11396,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11394,10 +11410,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11405,7 +11421,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>93</v>
@@ -11420,18 +11436,18 @@
         <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11479,7 +11495,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11500,10 +11516,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11514,10 +11530,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11525,7 +11541,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>93</v>
@@ -11540,17 +11556,17 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11599,7 +11615,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11620,10 +11636,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11634,10 +11650,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11660,19 +11676,17 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>322</v>
+        <v>107</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11721,7 +11735,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11742,10 +11756,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11756,10 +11770,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11782,19 +11796,19 @@
         <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>107</v>
+        <v>327</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11843,7 +11857,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11864,10 +11878,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11878,21 +11892,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>517</v>
+        <v>82</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
@@ -11901,22 +11915,22 @@
         <v>82</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>256</v>
+        <v>107</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>518</v>
+        <v>337</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>519</v>
+        <v>338</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>520</v>
+        <v>339</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>521</v>
+        <v>340</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11941,11 +11955,13 @@
         <v>82</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y79" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z79" t="s" s="2">
-        <v>522</v>
+        <v>82</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -11963,13 +11979,13 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>516</v>
+        <v>341</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
@@ -11981,31 +11997,31 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>523</v>
+        <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>524</v>
+        <v>342</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>525</v>
+        <v>343</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>526</v>
+        <v>82</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -12024,19 +12040,19 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>528</v>
+        <v>261</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12061,13 +12077,11 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>82</v>
+        <v>527</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -12085,7 +12099,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12103,27 +12117,27 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>82</v>
+        <v>531</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12134,7 +12148,7 @@
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -12146,18 +12160,20 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>256</v>
+        <v>533</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N81" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="N81" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>82</v>
       </c>
@@ -12181,13 +12197,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>539</v>
+        <v>82</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>540</v>
+        <v>82</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12205,13 +12221,13 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>82</v>
@@ -12223,27 +12239,27 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>541</v>
+        <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>544</v>
+        <v>82</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12266,20 +12282,18 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>549</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12306,10 +12320,10 @@
         <v>163</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12327,7 +12341,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12345,27 +12359,27 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>82</v>
+        <v>546</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>82</v>
+        <v>549</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12388,18 +12402,20 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>555</v>
+        <v>261</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="O83" s="2"/>
+        <v>553</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>554</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12423,13 +12439,13 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>82</v>
+        <v>555</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>82</v>
+        <v>556</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12447,7 +12463,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12465,27 +12481,27 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>559</v>
+        <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>562</v>
+        <v>82</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12499,7 +12515,7 @@
         <v>93</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>82</v>
@@ -12508,16 +12524,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12567,7 +12583,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12585,27 +12601,27 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>571</v>
+        <v>567</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12616,10 +12632,10 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>82</v>
@@ -12628,20 +12644,18 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>577</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12689,45 +12703,45 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>578</v>
+        <v>105</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>82</v>
+        <v>573</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>82</v>
+        <v>576</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12738,7 +12752,7 @@
         <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>82</v>
@@ -12750,16 +12764,20 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>107</v>
+        <v>578</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>108</v>
+        <v>579</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
+        <v>580</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>582</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12807,19 +12825,19 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>110</v>
+        <v>577</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>82</v>
+        <v>583</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -12828,10 +12846,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>82</v>
+        <v>584</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>111</v>
+        <v>585</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12842,21 +12860,21 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>82</v>
@@ -12868,17 +12886,15 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12927,19 +12943,19 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -12962,14 +12978,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>584</v>
+        <v>113</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12982,26 +12998,24 @@
         <v>82</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>585</v>
+        <v>115</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>586</v>
+        <v>116</v>
       </c>
       <c r="N88" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O88" t="s" s="2">
-        <v>214</v>
-      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -13049,7 +13063,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>587</v>
+        <v>121</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13073,7 +13087,7 @@
         <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13091,26 +13105,26 @@
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>82</v>
+        <v>589</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>589</v>
+        <v>114</v>
       </c>
       <c r="L89" t="s" s="2">
         <v>590</v>
@@ -13118,8 +13132,12 @@
       <c r="M89" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+      <c r="N89" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13167,19 +13185,19 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>592</v>
+        <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -13188,10 +13206,10 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>593</v>
+        <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>594</v>
+        <v>196</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13202,10 +13220,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13228,13 +13246,13 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13285,7 +13303,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13294,7 +13312,7 @@
         <v>93</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>105</v>
@@ -13306,10 +13324,10 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13320,10 +13338,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13346,20 +13364,16 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>256</v>
+        <v>594</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="N91" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="O91" t="s" s="2">
-        <v>603</v>
-      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13383,13 +13397,13 @@
         <v>82</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>604</v>
+        <v>82</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>605</v>
+        <v>82</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -13407,7 +13421,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13416,7 +13430,7 @@
         <v>93</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>82</v>
+        <v>597</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>105</v>
@@ -13425,13 +13439,13 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>606</v>
+        <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>525</v>
+        <v>603</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13442,10 +13456,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13456,7 +13470,7 @@
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>82</v>
@@ -13468,19 +13482,19 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -13505,13 +13519,13 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13529,13 +13543,13 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>82</v>
@@ -13547,13 +13561,13 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13564,10 +13578,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13578,7 +13592,7 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>82</v>
@@ -13590,17 +13604,19 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="N93" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13625,13 +13641,13 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>82</v>
+        <v>618</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>82</v>
+        <v>619</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13649,13 +13665,13 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>82</v>
@@ -13667,13 +13683,13 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>82</v>
+        <v>611</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>82</v>
+        <v>612</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>620</v>
+        <v>530</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13684,10 +13700,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13710,7 +13726,7 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>107</v>
+        <v>621</v>
       </c>
       <c r="L94" t="s" s="2">
         <v>622</v>
@@ -13719,7 +13735,9 @@
         <v>623</v>
       </c>
       <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+      <c r="O94" t="s" s="2">
+        <v>624</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
       </c>
@@ -13767,7 +13785,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13788,10 +13806,10 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>593</v>
+        <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13802,10 +13820,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13816,7 +13834,7 @@
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>82</v>
@@ -13825,10 +13843,10 @@
         <v>82</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>626</v>
+        <v>107</v>
       </c>
       <c r="L95" t="s" s="2">
         <v>627</v>
@@ -13836,9 +13854,7 @@
       <c r="M95" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="N95" t="s" s="2">
-        <v>629</v>
-      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13887,13 +13903,13 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>82</v>
@@ -13908,10 +13924,10 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>630</v>
+        <v>598</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13922,10 +13938,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13948,16 +13964,16 @@
         <v>94</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14007,7 +14023,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14028,10 +14044,10 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -14042,10 +14058,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14059,7 +14075,7 @@
         <v>81</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>82</v>
@@ -14068,20 +14084,18 @@
         <v>94</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>573</v>
+        <v>638</v>
       </c>
       <c r="L97" t="s" s="2">
         <v>639</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="O97" t="s" s="2">
         <v>641</v>
       </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -14129,7 +14143,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14141,19 +14155,19 @@
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AN97" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14164,10 +14178,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14178,28 +14192,32 @@
         <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>107</v>
+        <v>578</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>108</v>
+        <v>644</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
+        <v>644</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>646</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
@@ -14247,19 +14265,19 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>110</v>
+        <v>643</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>82</v>
+        <v>647</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>82</v>
@@ -14268,10 +14286,10 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>82</v>
+        <v>648</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>111</v>
+        <v>649</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14282,21 +14300,21 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>82</v>
@@ -14308,17 +14326,15 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N99" s="2"/>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -14367,19 +14383,19 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>82</v>
@@ -14402,14 +14418,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>584</v>
+        <v>113</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14422,26 +14438,24 @@
         <v>82</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>585</v>
+        <v>115</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>586</v>
+        <v>116</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O100" t="s" s="2">
-        <v>214</v>
-      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
@@ -14489,7 +14503,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>587</v>
+        <v>121</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14513,7 +14527,7 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14524,45 +14538,45 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>82</v>
+        <v>589</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I101" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J101" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>256</v>
+        <v>114</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>649</v>
+        <v>590</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>650</v>
+        <v>591</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>651</v>
+        <v>117</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>652</v>
+        <v>219</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14587,13 +14601,13 @@
         <v>82</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>82</v>
@@ -14611,34 +14625,34 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>648</v>
+        <v>592</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>653</v>
+        <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>350</v>
+        <v>196</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>82</v>
@@ -14646,10 +14660,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14657,7 +14671,7 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>93</v>
@@ -14672,19 +14686,19 @@
         <v>94</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="O102" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
@@ -14712,10 +14726,10 @@
         <v>155</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>659</v>
+        <v>350</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>660</v>
+        <v>351</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>82</v>
@@ -14733,16 +14747,16 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>661</v>
+        <v>82</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>105</v>
@@ -14751,27 +14765,27 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>441</v>
+        <v>354</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>442</v>
+        <v>355</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>82</v>
+        <v>356</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14791,22 +14805,22 @@
         <v>82</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>256</v>
+        <v>660</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>500</v>
+        <v>441</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14834,10 +14848,10 @@
         <v>155</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>501</v>
+        <v>664</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>502</v>
+        <v>665</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
@@ -14855,7 +14869,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14864,7 +14878,7 @@
         <v>93</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>105</v>
@@ -14873,19 +14887,19 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>82</v>
+        <v>667</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>196</v>
+        <v>446</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>504</v>
+        <v>447</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
     </row>
     <row r="104" hidden="true">
@@ -14897,17 +14911,17 @@
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>517</v>
+        <v>82</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>82</v>
@@ -14916,19 +14930,19 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>518</v>
+        <v>669</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>519</v>
+        <v>670</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>520</v>
+        <v>671</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>521</v>
+        <v>505</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -14956,10 +14970,10 @@
         <v>155</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>669</v>
+        <v>506</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>522</v>
+        <v>507</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -14983,10 +14997,10 @@
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>82</v>
+        <v>672</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>105</v>
@@ -14995,31 +15009,31 @@
         <v>82</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>523</v>
+        <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>524</v>
+        <v>196</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>525</v>
+        <v>509</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>526</v>
+        <v>82</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -15038,19 +15052,19 @@
         <v>82</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>83</v>
+        <v>261</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>671</v>
+        <v>523</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>672</v>
+        <v>524</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>576</v>
+        <v>525</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>577</v>
+        <v>526</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -15075,13 +15089,13 @@
         <v>82</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>82</v>
+        <v>674</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>82</v>
+        <v>527</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -15099,7 +15113,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15117,23 +15131,145 @@
         <v>82</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>579</v>
+        <v>529</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>580</v>
+        <v>530</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP105" t="s" s="2">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP106" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP105">
+  <autoFilter ref="A1:AP106">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15143,7 +15279,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI104">
+  <conditionalFormatting sqref="A2:AI105">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T12:38:35+00:00</t>
+    <t>2025-07-07T15:58:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1350,7 +1350,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -2459,7 +2459,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="191.30859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="179.3984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T15:58:33+00:00</t>
+    <t>2025-07-07T16:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
